--- a/03_Group_comparisons/Proteome_T2/c_data/01_design_contrasts.xlsx
+++ b/03_Group_comparisons/Proteome_T2/c_data/01_design_contrasts.xlsx
@@ -78,13 +78,13 @@
     <t>role</t>
   </si>
   <si>
-    <t>How the contrast is read: primary, secondary, descriptive, or floor (the baseline group difference).</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>Feature level: proteins, sets or modules.</t>
+    <t>How the contrast is read: primary, secondary, descriptive, or baseline_reference (the baseline group difference).</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>What a correlation is estimated within.</t>
   </si>
   <si>
     <t>correlation</t>
@@ -162,7 +162,7 @@
     <t>Baseline_C1vC2</t>
   </si>
   <si>
-    <t>floor</t>
+    <t>baseline_reference</t>
   </si>
   <si>
     <t>Trained_C1vC2 = C1_T2 - C2_T2</t>
@@ -204,7 +204,7 @@
     <t>01_Processing/03_Quantification/c_data/proteins.rds</t>
   </si>
   <si>
-    <t>34ef12f3ddbea70e6840925bab8692c5</t>
+    <t>765866aefeddf8c95296dd4824ecca44</t>
   </si>
   <si>
     <t>groups</t>
@@ -213,7 +213,7 @@
     <t>02_Groups/Proteome_T2/c_data/groups.rds</t>
   </si>
   <si>
-    <t>66d4ea9705e4ef793c273e79ff366700</t>
+    <t>f639ff53292f94c9416c61f032adb567</t>
   </si>
   <si>
     <t>BiocGenerics</t>
